--- a/issuesNRISS/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/issuesNRISS/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T08:17:10+00:00</t>
+    <t>2026-06-18T14:12:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -797,7 +797,7 @@
 </t>
   </si>
   <si>
-    <t>Number of Study Related Series</t>
+    <t>Nombre de séries</t>
   </si>
   <si>
     <t>Number of Series in the Study. This value given may be larger than the number of series elements this Resource contains due to resource availability, security, or other factors. This element should be present if any series elements are present.</t>
@@ -4384,7 +4384,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>245</v>
       </c>
@@ -4403,7 +4403,7 @@
         <v>89</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>78</v>
